--- a/model results.xlsx
+++ b/model results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\code\llm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{961EE598-BD8B-4243-AA61-53A576B9FDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6BB7A7-1105-4390-8431-7B878CBAFDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1898E347-8C22-4F6E-9186-A0F0FC610726}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$L$16:$S$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$L$16:$R$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>batch size</t>
   </si>
@@ -105,6 +105,30 @@
   </si>
   <si>
     <t>TODO L17 should match value in final run</t>
+  </si>
+  <si>
+    <t>Final Validation Loss</t>
+  </si>
+  <si>
+    <t>Weight Decay</t>
+  </si>
+  <si>
+    <t>Head Count</t>
+  </si>
+  <si>
+    <t>Block Count</t>
+  </si>
+  <si>
+    <t>Batch Size</t>
+  </si>
+  <si>
+    <t>Embedding Size</t>
+  </si>
+  <si>
+    <t>Learning Rate</t>
+  </si>
+  <si>
+    <t>Steps</t>
   </si>
 </sst>
 </file>
@@ -112,8 +136,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
-    <numFmt numFmtId="171" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -152,17 +176,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,44 +536,44 @@
     <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9" customWidth="1"/>
-    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
       <c r="L4" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M4" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N4" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="O4" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="P4" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R4" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="S4" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="L5" s="5">
-        <v>3.6880000000000002</v>
+      <c r="L5" s="6">
+        <v>10000</v>
       </c>
       <c r="M5">
         <v>0.05</v>
@@ -559,16 +590,16 @@
       <c r="Q5" s="3">
         <v>768</v>
       </c>
-      <c r="R5" s="9">
+      <c r="R5" s="7">
         <v>1E-4</v>
       </c>
-      <c r="S5" s="7">
+      <c r="S5" s="4">
+        <v>3.6880000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="L6" s="6">
         <v>10000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="L6" s="5">
-        <v>3.77</v>
       </c>
       <c r="M6">
         <v>0.1</v>
@@ -585,19 +616,19 @@
       <c r="Q6">
         <v>768</v>
       </c>
-      <c r="R6" s="9">
+      <c r="R6" s="7">
         <v>1E-4</v>
       </c>
-      <c r="S6" s="7">
-        <v>10000</v>
+      <c r="S6" s="4">
+        <v>3.77</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="5">
-        <v>3.79</v>
+      <c r="L7" s="6">
+        <v>10000</v>
       </c>
       <c r="M7">
         <v>0.05</v>
@@ -614,19 +645,19 @@
       <c r="Q7">
         <v>1024</v>
       </c>
-      <c r="R7" s="9">
+      <c r="R7" s="7">
         <v>1E-4</v>
       </c>
-      <c r="S7" s="7">
-        <v>10000</v>
+      <c r="S7" s="4">
+        <v>3.79</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="5">
-        <v>3.8250000000000002</v>
+      <c r="L8" s="6">
+        <v>10000</v>
       </c>
       <c r="M8">
         <v>0.1</v>
@@ -634,7 +665,7 @@
       <c r="N8">
         <v>12</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
@@ -643,19 +674,19 @@
       <c r="Q8">
         <v>768</v>
       </c>
-      <c r="R8" s="9">
+      <c r="R8" s="7">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="S8" s="7">
-        <v>10000</v>
+      <c r="S8" s="4">
+        <v>3.8250000000000002</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="5">
-        <v>4.05</v>
+      <c r="L9" s="6">
+        <v>10000</v>
       </c>
       <c r="M9">
         <v>0.1</v>
@@ -663,7 +694,7 @@
       <c r="N9">
         <v>8</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
@@ -672,19 +703,19 @@
       <c r="Q9">
         <v>512</v>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="7">
         <v>1E-4</v>
       </c>
-      <c r="S9" s="7">
-        <v>10000</v>
+      <c r="S9" s="4">
+        <v>4.05</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="L10" s="5">
-        <v>4.5199999999999996</v>
+      <c r="L10" s="6">
+        <v>10000</v>
       </c>
       <c r="M10" s="3">
         <v>0.1</v>
@@ -701,19 +732,19 @@
       <c r="Q10">
         <v>768</v>
       </c>
-      <c r="R10" s="9">
+      <c r="R10" s="7">
         <v>1E-4</v>
       </c>
-      <c r="S10" s="7">
-        <v>10000</v>
+      <c r="S10" s="4">
+        <v>4.5199999999999996</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="5">
-        <v>4.6100000000000003</v>
+      <c r="L11" s="6">
+        <v>10000</v>
       </c>
       <c r="M11">
         <v>0.1</v>
@@ -730,19 +761,19 @@
       <c r="Q11">
         <v>768</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="7">
         <v>1E-4</v>
       </c>
-      <c r="S11" s="7">
-        <v>10000</v>
+      <c r="S11" s="4">
+        <v>4.6100000000000003</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L12" s="5">
-        <v>6.73</v>
+      <c r="L12" s="6">
+        <v>10000</v>
       </c>
       <c r="M12">
         <v>0.05</v>
@@ -750,7 +781,7 @@
       <c r="N12">
         <v>12</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
@@ -759,55 +790,52 @@
       <c r="Q12">
         <v>768</v>
       </c>
-      <c r="R12" s="9">
+      <c r="R12" s="7">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="S12" s="7">
-        <v>10000</v>
+      <c r="S12" s="4">
+        <v>6.73</v>
       </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="L13" s="5"/>
-      <c r="O13" s="4"/>
+      <c r="L13" s="4"/>
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="L14" s="5"/>
-      <c r="O14" s="4"/>
+      <c r="L14" s="4"/>
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="L15" s="5"/>
-      <c r="O15" s="4"/>
+      <c r="L15" s="4"/>
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="L16" t="s">
-        <v>15</v>
-      </c>
-      <c r="M16" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16" t="s">
-        <v>2</v>
-      </c>
-      <c r="O16" t="s">
-        <v>3</v>
-      </c>
-      <c r="P16" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>4</v>
-      </c>
-      <c r="R16" t="s">
-        <v>5</v>
-      </c>
-      <c r="S16" t="s">
-        <v>7</v>
+        <v>29</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.25">
@@ -817,111 +845,111 @@
       <c r="I17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L17">
-        <v>3.3490000000000002</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="6">
+        <v>100000</v>
+      </c>
+      <c r="M17" s="8">
         <v>0.1</v>
       </c>
-      <c r="N17">
-        <v>12</v>
-      </c>
-      <c r="O17" s="4">
-        <v>12</v>
-      </c>
-      <c r="P17" s="4">
+      <c r="N17" s="8">
+        <v>12</v>
+      </c>
+      <c r="O17" s="8">
+        <v>12</v>
+      </c>
+      <c r="P17" s="8">
         <v>32</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="Q17" s="8">
         <v>768</v>
       </c>
       <c r="R17" s="9">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="S17" s="8">
+        <v>3.3490000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="L18" s="6">
         <v>100000</v>
       </c>
-    </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="L18">
-        <v>3.3519999999999999</v>
-      </c>
-      <c r="M18">
+      <c r="M18" s="8">
         <v>0.05</v>
       </c>
-      <c r="N18">
-        <v>12</v>
-      </c>
-      <c r="O18" s="4">
+      <c r="N18" s="8">
+        <v>12</v>
+      </c>
+      <c r="O18" s="8">
         <v>6</v>
       </c>
-      <c r="P18" s="4">
+      <c r="P18" s="8">
         <v>32</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="Q18" s="8">
         <v>768</v>
       </c>
       <c r="R18" s="9">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="S18" s="8">
-        <v>100000</v>
+        <v>3.3519999999999999</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
-      <c r="L19">
-        <v>3.4249999999999998</v>
-      </c>
-      <c r="M19">
+      <c r="L19" s="6">
+        <v>100000</v>
+      </c>
+      <c r="M19" s="8">
         <v>0.05</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="8">
         <v>16</v>
       </c>
-      <c r="O19">
-        <v>12</v>
-      </c>
-      <c r="P19">
+      <c r="O19" s="8">
+        <v>12</v>
+      </c>
+      <c r="P19" s="8">
         <v>32</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="8">
         <v>1024</v>
       </c>
       <c r="R19" s="9">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="S19" s="8">
+        <v>3.4249999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="F20" s="5"/>
+      <c r="L20" s="6">
         <v>100000</v>
       </c>
-    </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="F20" s="6"/>
-      <c r="L20" s="6">
-        <v>3.5368900000000001</v>
-      </c>
-      <c r="M20">
+      <c r="M20" s="8">
         <v>0.05</v>
       </c>
-      <c r="N20">
-        <v>12</v>
-      </c>
-      <c r="O20" s="4">
+      <c r="N20" s="8">
+        <v>12</v>
+      </c>
+      <c r="O20" s="8">
         <v>6</v>
       </c>
-      <c r="P20" s="4">
+      <c r="P20" s="8">
         <v>32</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="Q20" s="8">
         <v>768</v>
       </c>
       <c r="R20" s="9">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="S20" s="8">
-        <v>100000</v>
+      <c r="S20" s="10">
+        <v>3.5368900000000001</v>
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.25">
@@ -978,7 +1006,7 @@
       <c r="Q25">
         <v>768</v>
       </c>
-      <c r="R25" s="9">
+      <c r="R25" s="7">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="S25" t="s">

--- a/model results.xlsx
+++ b/model results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\code\llm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6BB7A7-1105-4390-8431-7B878CBAFDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4148695F-FC51-476D-A029-53EF92507314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1898E347-8C22-4F6E-9186-A0F0FC610726}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>batch size</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>Steps</t>
+  </si>
+  <si>
+    <t>perplexity</t>
   </si>
 </sst>
 </file>
@@ -528,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF43007-E69D-45D5-BD7A-20978983A979}">
-  <dimension ref="B4:S25"/>
+  <dimension ref="B4:S27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="43.28515625" bestFit="1" customWidth="1"/>
@@ -991,6 +994,9 @@
       <c r="J25" t="s">
         <v>19</v>
       </c>
+      <c r="L25">
+        <v>2.98</v>
+      </c>
       <c r="M25">
         <v>0.1</v>
       </c>
@@ -1011,6 +1017,15 @@
       </c>
       <c r="S25" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="K27" t="s">
+        <v>30</v>
+      </c>
+      <c r="L27">
+        <f>EXP(L25)</f>
+        <v>19.6878166447624</v>
       </c>
     </row>
   </sheetData>
